--- a/SGC-CKN/Excel/67bc18ea-f330-41e8-bb6a-a49cc9a45bd8_Cọc_khoan_nhồi_P7-59_D800_31-03-2026.xlsx
+++ b/SGC-CKN/Excel/67bc18ea-f330-41e8-bb6a-a49cc9a45bd8_Cọc_khoan_nhồi_P7-59_D800_31-03-2026.xlsx
@@ -1253,10 +1253,10 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-7.21</v>
+        <v>-6.5</v>
       </c>
       <c r="H11" s="5">
         <v>0.67</v>
@@ -1288,10 +1288,10 @@
         <v>34</v>
       </c>
       <c r="F12" s="9">
-        <v>-7.21</v>
+        <v>-6.5</v>
       </c>
       <c r="G12" s="9">
-        <v>-9.21</v>
+        <v>-8.5</v>
       </c>
       <c r="H12" s="9">
         <v>0.65</v>
@@ -1323,10 +1323,10 @@
         <v>38</v>
       </c>
       <c r="F13" s="13">
-        <v>-9.21</v>
+        <v>-8.5</v>
       </c>
       <c r="G13" s="13">
-        <v>-17.41</v>
+        <v>-16.7</v>
       </c>
       <c r="H13" s="13">
         <v>1.32</v>
@@ -1358,10 +1358,10 @@
         <v>42</v>
       </c>
       <c r="F14" s="16">
-        <v>-17.41</v>
+        <v>-16.7</v>
       </c>
       <c r="G14" s="16">
-        <v>-21.71</v>
+        <v>-21</v>
       </c>
       <c r="H14" s="16">
         <v>1.07</v>
@@ -1393,10 +1393,10 @@
         <v>46</v>
       </c>
       <c r="F15" s="19">
-        <v>-21.71</v>
+        <v>-21</v>
       </c>
       <c r="G15" s="19">
-        <v>-25.61</v>
+        <v>-24.9</v>
       </c>
       <c r="H15" s="19">
         <v>0.73</v>
@@ -1428,10 +1428,10 @@
         <v>50</v>
       </c>
       <c r="F16" s="22">
-        <v>-25.61</v>
+        <v>-24.9</v>
       </c>
       <c r="G16" s="22">
-        <v>-35.61</v>
+        <v>-34.9</v>
       </c>
       <c r="H16" s="22">
         <v>0.9</v>
@@ -1463,10 +1463,10 @@
         <v>54</v>
       </c>
       <c r="F17" s="25">
-        <v>-35.61</v>
+        <v>-34.9</v>
       </c>
       <c r="G17" s="25">
-        <v>-38.11</v>
+        <v>-37.4</v>
       </c>
       <c r="H17" s="25">
         <v>0.82</v>
@@ -1498,10 +1498,10 @@
         <v>58</v>
       </c>
       <c r="F18" s="28">
-        <v>-38.11</v>
+        <v>-37.4</v>
       </c>
       <c r="G18" s="28">
-        <v>-40.51</v>
+        <v>-39.8</v>
       </c>
       <c r="H18" s="28">
         <v>1.98</v>
@@ -1533,16 +1533,16 @@
         <v>62</v>
       </c>
       <c r="F19" s="31">
-        <v>-40.51</v>
+        <v>-39.8</v>
       </c>
       <c r="G19" s="31">
-        <v>-43.11</v>
+        <v>-42.41</v>
       </c>
       <c r="H19" s="31">
         <v>2.9</v>
       </c>
       <c r="I19" s="31">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="J19" s="34">
         <v>0.9</v>
@@ -1568,19 +1568,19 @@
         <v>66</v>
       </c>
       <c r="F20" s="35">
-        <v>-43.11</v>
+        <v>-42.41</v>
       </c>
       <c r="G20" s="35">
-        <v>-45.56</v>
+        <v>-44.85</v>
       </c>
       <c r="H20" s="35">
         <v>0.55</v>
       </c>
       <c r="I20" s="35">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="J20" s="12">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="K20" s="36" t="s">
         <v>30</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-7.21</v>
+        <v>-6.5</v>
       </c>
       <c r="G2" s="5">
         <v>0.67</v>
@@ -1764,10 +1764,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-7.21</v>
+        <v>-6.5</v>
       </c>
       <c r="F3" s="9">
-        <v>-9.21</v>
+        <v>-8.5</v>
       </c>
       <c r="G3" s="9">
         <v>0.65</v>
@@ -1793,10 +1793,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="13">
-        <v>-9.21</v>
+        <v>-8.5</v>
       </c>
       <c r="F4" s="13">
-        <v>-17.41</v>
+        <v>-16.7</v>
       </c>
       <c r="G4" s="13">
         <v>1.32</v>
@@ -1822,10 +1822,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-17.41</v>
+        <v>-16.7</v>
       </c>
       <c r="F5" s="16">
-        <v>-21.71</v>
+        <v>-21</v>
       </c>
       <c r="G5" s="16">
         <v>1.07</v>
@@ -1851,10 +1851,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-21.71</v>
+        <v>-21</v>
       </c>
       <c r="F6" s="19">
-        <v>-25.61</v>
+        <v>-24.9</v>
       </c>
       <c r="G6" s="19">
         <v>0.73</v>
@@ -1880,10 +1880,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-25.61</v>
+        <v>-24.9</v>
       </c>
       <c r="F7" s="22">
-        <v>-35.61</v>
+        <v>-34.9</v>
       </c>
       <c r="G7" s="22">
         <v>0.9</v>
@@ -1909,10 +1909,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-35.61</v>
+        <v>-34.9</v>
       </c>
       <c r="F8" s="25">
-        <v>-38.11</v>
+        <v>-37.4</v>
       </c>
       <c r="G8" s="25">
         <v>0.82</v>
@@ -1938,10 +1938,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-38.11</v>
+        <v>-37.4</v>
       </c>
       <c r="F9" s="28">
-        <v>-40.51</v>
+        <v>-39.8</v>
       </c>
       <c r="G9" s="28">
         <v>1.98</v>
@@ -1967,16 +1967,16 @@
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-40.51</v>
+        <v>-39.8</v>
       </c>
       <c r="F10" s="31">
-        <v>-43.11</v>
+        <v>-42.41</v>
       </c>
       <c r="G10" s="31">
         <v>2.9</v>
       </c>
       <c r="H10" s="31">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="I10" s="34">
         <v>0.9</v>
@@ -1996,19 +1996,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="35">
-        <v>-43.11</v>
+        <v>-42.41</v>
       </c>
       <c r="F11" s="35">
-        <v>-45.56</v>
+        <v>-44.85</v>
       </c>
       <c r="G11" s="35">
         <v>0.55</v>
       </c>
       <c r="H11" s="35">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="I11" s="12">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2025,10 +2025,10 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
-        <v>-45.56</v>
+        <v>-44.85</v>
       </c>
       <c r="G12" s="40">
         <v>11.58</v>
